--- a/conversational-search-cost-calculator.xlsx
+++ b/conversational-search-cost-calculator.xlsx
@@ -18,8 +18,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.000000"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.000000"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
   <fonts count="8">
@@ -59,7 +59,7 @@
       <sz val="13"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -93,7 +93,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E8DCFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE3DC"/>
       </patternFill>
     </fill>
   </fills>
@@ -109,7 +119,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -130,22 +140,30 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
+    <xf numFmtId="165" fontId="5" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="6" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -527,14 +545,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -554,7 +572,7 @@
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Monthly site visitors</t>
+          <t>Monthly searches</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
@@ -562,14 +580,14 @@
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>enter your expected monthly traffic</t>
+          <t>every search auto-engages Turn 1 (100%)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Engagement rate (CTR, %)</t>
+          <t>Turn 2+3 engagement rate (%)</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
@@ -577,633 +595,879 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>percent of visitors that interact with the agent</t>
+          <t>% of searches where the user continues past Turn 1</t>
         </is>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Avg input tokens per LLM call</t>
+          <t>Avg input tokens / LLM call — Turn 1</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>7500</v>
+        <v>4251</v>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>DEFAULT — cascade across 6 calls (T1/T2/T3 tool-decision + response); see Notes Defaults Provenance</t>
+          <t>T1 cascade avg: 90% × 1-call(4,060) + 10% × 2-call-avg(5,110)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Total output tokens per conversation</t>
+          <t>Avg input tokens / LLM call — Turn 2+3</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>1159</v>
+        <v>8544</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>DEFAULT — sum across turns: T1=105 + T2=527 + T3=527 (T3 extrapolated; from post-tightening benchmark sk-multi-run-postfix-20260511)</t>
+          <t>T2+T3 cascade avg across 4 calls (T2a=6,295 / T2b=8,425 / T3a=8,982 / T3b=11,082)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>LLM calls per turn</t>
+          <t>T1 output tokens (always)</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>2</v>
+        <v>205</v>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>DEFAULT — measured median; max=2 per max_tool_calls_per_turn config</t>
+          <t>tool-call output (~100) + brief response (~105) per benchmark</t>
         </is>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Guardrails enabled</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
+          <t>T2+T3 output tokens (additional, when engaged)</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>1254</v>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Yes / No</t>
+          <t>T2 (627) + T3 (627) — each turn: tool-call (~100) + response (~527)</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Guardrail policy mix</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Content only</t>
-        </is>
+          <t>LLM calls — T1 (avg)</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>1.1</v>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>"Content only" | "Content + PII" | "Content + PII + Grounding"</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>LOCKED CONSTANTS  (do not change)</t>
+          <t>most T1 = 1 call; ~10% take 2 (retries / long-form)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>LLM calls — T2+T3 combined (when engaged)</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>T2: 2 calls (tool-decision + response) + T3: 2 calls</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Guardrails enabled</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Yes / No</t>
         </is>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>Conversation length (turns)</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n">
-        <v>3</v>
+          <t>Guardrail policy mix</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Content only</t>
+        </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>locked per spec — typical 3-turn search interaction</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>Sonnet 4.6 input price ($/M tokens)</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>standard input, AWS Bedrock 2026-05-14</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="18" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Sonnet 4.6 output price ($/M tokens)</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n">
-        <v>15</v>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>standard output, AWS Bedrock 2026-05-14</t>
+          <t>"Content only" | "Content + PII" | "Content + PII + Grounding"</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>LOCKED CONSTANTS  (do not change)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>5m cache write price ($/M tokens)</t>
+          <t>Sonnet 4.6 input price ($/M tokens)</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>1.25x input — Anthropic prompt caching</t>
+          <t>standard input, AWS Bedrock 2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>5m cache read price ($/M tokens)</t>
+          <t>Sonnet 4.6 output price ($/M tokens)</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>0.3</v>
+        <v>15</v>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>0.10x input — Anthropic prompt caching</t>
+          <t>standard output</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Cached prefix tokens</t>
+          <t>5m cache write price ($/M tokens)</t>
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>4030</v>
+        <v>3.75</v>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>system prompt (3,098 measured via tiktoken on prompts.py code) + search_products_tool schema (932 via convert_to_openai_tool); production Langfuse-hosted prompt may differ</t>
+          <t>1.25x input — Anthropic prompt caching</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Chars per token (approx)</t>
+          <t>5m cache read price ($/M tokens)</t>
         </is>
       </c>
       <c r="B19" s="7" t="n">
-        <v>4</v>
+        <v>0.3</v>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>rough English heuristic for guardrail text-unit math</t>
+          <t>0.10x input — Anthropic prompt caching</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Guardrail rate — Content only ($/1K)</t>
+          <t>Cached prefix tokens</t>
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>0.75</v>
+        <v>4030</v>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>content filters / denied topics / word filters</t>
+          <t>system prompt (3,098 tiktoken) + search_products_tool schema (932); production Langfuse prompt may differ</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Guardrail rate — Content+PII ($/1K)</t>
+          <t>Chars per token (approx)</t>
         </is>
       </c>
       <c r="B21" s="7" t="n">
-        <v>0.85</v>
+        <v>4</v>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>adds $0.10/1K for PII policy</t>
+          <t>English heuristic for guardrail text-unit math</t>
         </is>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
+          <t>Guardrail rate — Content only ($/1K)</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>content filters / denied topics / word filters</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Guardrail rate — Content+PII ($/1K)</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>+ $0.10/1K for PII policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
           <t>Guardrail rate — Content+PII+Gnd ($/1K)</t>
         </is>
       </c>
-      <c r="B22" s="7" t="n">
+      <c r="B24" s="7" t="n">
         <v>0.95</v>
       </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>adds $0.10/1K for contextual grounding</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>DERIVED — PER CONVERSATION</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>% of total</t>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>+ $0.10/1K for contextual grounding</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Total LLM calls per conversation</t>
-        </is>
-      </c>
-      <c r="B25" s="10">
-        <f>B13*B8</f>
-        <v/>
+          <t>Cache TTL (minutes)</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>5</v>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>turns x calls/turn</t>
+          <t>Anthropic 5m cache — shared across users hitting the same cached prefix</t>
         </is>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Total output tokens per conversation</t>
-        </is>
-      </c>
-      <c r="B26" s="10">
-        <f>B7</f>
-        <v/>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>from B7 input (sum across turns)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="18" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Dynamic input tokens per call</t>
-        </is>
-      </c>
-      <c r="B27" s="10">
-        <f>B6-B18</f>
-        <v/>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>input per call minus cached prefix</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="18" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Cache write cost — 1st call ($)</t>
-        </is>
-      </c>
-      <c r="B28" s="11">
-        <f>B18*B16/1000000</f>
-        <v/>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>cached prefix written once per conversation</t>
+          <t>5-min windows per month</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>8640</v>
+      </c>
+      <c r="C26" s="5">
+        <f> 30 days × 24 hours × 12 windows/hour</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>DERIVED — COST DECOMPOSITION</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>% of monthly</t>
         </is>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Cache read cost — remaining calls ($)</t>
-        </is>
-      </c>
-      <c r="B29" s="11">
-        <f>B18*B17/1000000*(B25-1)</f>
+          <t>Effective cache write fraction (per search)</t>
+        </is>
+      </c>
+      <c r="B29" s="10">
+        <f>MIN(B4,B26)/B4</f>
         <v/>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>cached prefix re-read on calls 2..N</t>
+          <t>uniform-distribution model: writes/month = MIN(searches, 5-min windows)</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Dynamic input cost ($)</t>
+          <t>T1 dynamic input tokens per call</t>
         </is>
       </c>
       <c r="B30" s="11">
-        <f>B27*B25*B14/1000000</f>
-        <v/>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>non-cached tokens x all calls x input price</t>
-        </is>
+        <f>B6-B20</f>
+        <v/>
+      </c>
+      <c r="C30" s="5">
+        <f> B6 avg − cached prefix</f>
+        <v/>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Output cost ($)</t>
+          <t>T2+T3 dynamic input tokens per call</t>
         </is>
       </c>
       <c r="B31" s="11">
-        <f>B26*B15/1000000</f>
-        <v/>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>total output tokens x output price</t>
-        </is>
+        <f>B7-B20</f>
+        <v/>
+      </c>
+      <c r="C31" s="5">
+        <f> B7 avg − cached prefix</f>
+        <v/>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>LLM cost per conversation ($)</t>
-        </is>
-      </c>
-      <c r="B32" s="11">
-        <f>SUM(B28:B31)</f>
+          <t>Active guardrail rate ($/1K text units)</t>
+        </is>
+      </c>
+      <c r="B32" s="12">
+        <f>IF(B12="Yes",IF(B13="Content only",B22,IF(B13="Content + PII",B23,B24)),0)</f>
         <v/>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>cache write + cache reads + dynamic input + output</t>
-        </is>
-      </c>
-      <c r="D32" s="12">
-        <f>B32/B36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Active guardrail rate ($/1K text units)</t>
-        </is>
-      </c>
-      <c r="B33" s="13">
-        <f>IF(B9="Yes",IF(B10="Content only",B20,IF(B10="Content + PII",B21,B22)),0)</f>
-        <v/>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
           <t>0 if guardrails disabled; else from policy mix selection</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="18" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Guardrail text units per conversation</t>
-        </is>
-      </c>
-      <c r="B34" s="13">
-        <f>(B25*B6*B19+B26*B19)/1000</f>
-        <v/>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>(input chars + output chars) / 1000 — see Notes for heuristic</t>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>Cost per search — Turn 1 only (ALWAYS incurred)</t>
         </is>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Guardrail cost per conversation ($)</t>
-        </is>
-      </c>
-      <c r="B35" s="11">
-        <f>B34*B33/1000</f>
+          <t>T1 first-call cache cost ($)</t>
+        </is>
+      </c>
+      <c r="B35" s="14">
+        <f>(B29*B18 + (1-B29)*B19) * B20 / 1000000</f>
         <v/>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>text_units x rate / 1000 (B33 is $/1K text units); 0 if guardrails disabled</t>
-        </is>
-      </c>
-      <c r="D35" s="12">
-        <f>B35/B36</f>
-        <v/>
+          <t>first call: write if cache cold, read if warm — depends on cache sharing</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
-      <c r="A36" s="14" t="inlineStr">
-        <is>
-          <t>TOTAL cost per conversation ($)</t>
-        </is>
-      </c>
-      <c r="B36" s="15">
-        <f>B32+B35</f>
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>T1 subsequent-calls cache cost ($)</t>
+        </is>
+      </c>
+      <c r="B36" s="14">
+        <f>MAX(B10-1, 0) * B19 * B20 / 1000000</f>
         <v/>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>LLM cost + guardrail cost</t>
-        </is>
-      </c>
-      <c r="D36" s="16">
-        <f>B36/B36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="17" t="inlineStr">
-        <is>
-          <t>MONTHLY TOTALS</t>
+          <t>subsequent T1 calls (if 2-call path) — cache warm from first call</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>T1 dynamic input cost ($)</t>
+        </is>
+      </c>
+      <c r="B37" s="14">
+        <f>B30 * B10 * B16 / 1000000</f>
+        <v/>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>T1 dyn per call × T1 calls × input rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>T1 output cost ($)</t>
+        </is>
+      </c>
+      <c r="B38" s="14">
+        <f>B8 * B17 / 1000000</f>
+        <v/>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>T1 total output × output rate</t>
         </is>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Conversations per month</t>
-        </is>
-      </c>
-      <c r="B39" s="10">
-        <f>B4*B5/100</f>
-        <v/>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>visitors x CTR% / 100</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="18" t="inlineStr">
+          <t>T1 LLM cost subtotal ($)</t>
+        </is>
+      </c>
+      <c r="B39" s="14">
+        <f>SUM(B35:B38)</f>
+        <v/>
+      </c>
+      <c r="C39" s="5">
+        <f> first-call cache + subsequent-cache + dyn input + output</f>
+        <v/>
+      </c>
+      <c r="D39" s="15">
+        <f>B39*B4/B59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>T1 guardrail text units</t>
+        </is>
+      </c>
+      <c r="B40" s="12">
+        <f>(B10*B6*B21 + B8*B21) / 1000</f>
+        <v/>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>(T1 total input chars + output chars) / 1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>T1 guardrail cost ($)</t>
+        </is>
+      </c>
+      <c r="B41" s="14">
+        <f>B40 * B32 / 1000</f>
+        <v/>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>T1 text units × rate / 1000</t>
+        </is>
+      </c>
+      <c r="D41" s="15">
+        <f>B41*B4/B59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL T1 cost per search (always)</t>
+        </is>
+      </c>
+      <c r="B42" s="17">
+        <f>B39 + B41</f>
+        <v/>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>T1 LLM + T1 guardrail — every search pays this</t>
+        </is>
+      </c>
+      <c r="D42" s="15">
+        <f>B42*B4/B59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="18" t="inlineStr">
+        <is>
+          <t>Cost per search — Turn 2+3 ADDITIONAL (only when engaged)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>T2+T3 cache reads cost ($)</t>
+        </is>
+      </c>
+      <c r="B45" s="14">
+        <f>B11 * B19 * B20 / 1000000</f>
+        <v/>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>all T2+T3 calls are cache reads (warm from T1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>T2+T3 dynamic input cost ($)</t>
+        </is>
+      </c>
+      <c r="B46" s="14">
+        <f>B31 * B11 * B16 / 1000000</f>
+        <v/>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>T2+T3 dyn per call × T2+T3 calls × input rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>T2+T3 output cost ($)</t>
+        </is>
+      </c>
+      <c r="B47" s="14">
+        <f>B9 * B17 / 1000000</f>
+        <v/>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>T2+T3 additional output × output rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>T2+T3 LLM cost subtotal ($)</t>
+        </is>
+      </c>
+      <c r="B48" s="14">
+        <f>SUM(B45:B47)</f>
+        <v/>
+      </c>
+      <c r="C48" s="5">
+        <f> cache reads + dyn input + output</f>
+        <v/>
+      </c>
+      <c r="D48" s="15">
+        <f>B48*B4*(B5/100)/B59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>T2+T3 guardrail text units</t>
+        </is>
+      </c>
+      <c r="B49" s="12">
+        <f>(B11*B7*B21 + B9*B21) / 1000</f>
+        <v/>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>(T2+T3 total input chars + output chars) / 1000</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>T2+T3 guardrail cost ($)</t>
+        </is>
+      </c>
+      <c r="B50" s="14">
+        <f>B49 * B32 / 1000</f>
+        <v/>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>T2+T3 text units × rate / 1000</t>
+        </is>
+      </c>
+      <c r="D50" s="15">
+        <f>B50*B4*(B5/100)/B59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1">
+      <c r="A51" s="16" t="inlineStr">
+        <is>
+          <t>TOTAL additional cost per engaged search</t>
+        </is>
+      </c>
+      <c r="B51" s="17">
+        <f>B48 + B50</f>
+        <v/>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>incurred only on engaged searches (B5%)</t>
+        </is>
+      </c>
+      <c r="D51" s="15">
+        <f>B51*B4*(B5/100)/B59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="19" t="inlineStr">
+        <is>
+          <t>COMPOSED COST PER SEARCH (weighted by engagement)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1">
+      <c r="A54" s="16" t="inlineStr">
+        <is>
+          <t>Composed cost per search ($)</t>
+        </is>
+      </c>
+      <c r="B54" s="17">
+        <f>B42 + (B5/100)*B51</f>
+        <v/>
+      </c>
+      <c r="C54" s="5">
+        <f> T1 cost (always) + engagement% × T2+T3 cost (when engaged)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="19" t="inlineStr">
+        <is>
+          <t>MONTHLY TOTALS</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="18" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>T1 cost (across all searches) ($)</t>
+        </is>
+      </c>
+      <c r="B57" s="20">
+        <f>B4 * B42</f>
+        <v/>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>monthly searches × T1 cost per search</t>
+        </is>
+      </c>
+      <c r="D57" s="15">
+        <f>B57/B59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" ht="18" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>T2+T3 additional cost (engaged only) ($)</t>
+        </is>
+      </c>
+      <c r="B58" s="20">
+        <f>B4 * (B5/100) * B51</f>
+        <v/>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>engaged searches × T2+T3 cost per engaged search</t>
+        </is>
+      </c>
+      <c r="D58" s="15">
+        <f>B58/B59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59" ht="22" customHeight="1">
+      <c r="A59" s="21" t="inlineStr">
         <is>
           <t>TOTAL MONTHLY COST ($)</t>
         </is>
       </c>
-      <c r="B40" s="19">
-        <f>B39*B36</f>
-        <v/>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>conversations x cost per conversation</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="20" customHeight="1">
-      <c r="A42" s="17" t="inlineStr">
-        <is>
-          <t>SENSITIVITY TABLE — Monthly Cost by Visitors x CTR</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="20" t="inlineStr">
-        <is>
-          <t>Visitors \ CTR</t>
-        </is>
-      </c>
-      <c r="B43" s="21" t="inlineStr">
-        <is>
-          <t>1% CTR</t>
-        </is>
-      </c>
-      <c r="C43" s="21" t="inlineStr">
-        <is>
-          <t>5% CTR</t>
-        </is>
-      </c>
-      <c r="D43" s="21" t="inlineStr">
-        <is>
-          <t>10% CTR</t>
-        </is>
-      </c>
-      <c r="E43" s="21" t="inlineStr">
-        <is>
-          <t>15% CTR</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="18" customHeight="1">
-      <c r="A44" s="22" t="n">
+      <c r="B59" s="22">
+        <f>B4 * B54</f>
+        <v/>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>monthly searches × composed cost per search</t>
+        </is>
+      </c>
+      <c r="D59" s="23">
+        <f>B59/B59</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="19" t="inlineStr">
+        <is>
+          <t>SENSITIVITY TABLE — Monthly Cost by Searches × Engagement</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="24" t="inlineStr">
+        <is>
+          <t>Searches \ Engagement</t>
+        </is>
+      </c>
+      <c r="B63" s="25" t="inlineStr">
+        <is>
+          <t>1% engaged</t>
+        </is>
+      </c>
+      <c r="C63" s="25" t="inlineStr">
+        <is>
+          <t>5% engaged</t>
+        </is>
+      </c>
+      <c r="D63" s="25" t="inlineStr">
+        <is>
+          <t>10% engaged</t>
+        </is>
+      </c>
+      <c r="E63" s="25" t="inlineStr">
+        <is>
+          <t>15% engaged</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="18" customHeight="1">
+      <c r="A64" s="26" t="n">
         <v>10000</v>
       </c>
-      <c r="B44" s="23">
-        <f>10000*1/100*$B$36</f>
-        <v/>
-      </c>
-      <c r="C44" s="23">
-        <f>10000*5/100*$B$36</f>
-        <v/>
-      </c>
-      <c r="D44" s="23">
-        <f>10000*10/100*$B$36</f>
-        <v/>
-      </c>
-      <c r="E44" s="23">
-        <f>10000*15/100*$B$36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45" ht="18" customHeight="1">
-      <c r="A45" s="22" t="n">
+      <c r="B64" s="27">
+        <f>10000 * ((((((MIN(10000,$B$26)/10000)*$B$18 + (1-(MIN(10000,$B$26)/10000))*$B$19) * $B$20 / 1000000) + (MAX($B$10-1, 0) * $B$19 * $B$20 / 1000000) + ($B$30 * $B$10 * $B$16 / 1000000) + ($B$8 * $B$17 / 1000000)) + ((($B$10*$B$6*$B$21 + $B$8*$B$21) / 1000) * $B$32 / 1000)) + (1/100) * ($B$51))</f>
+        <v/>
+      </c>
+      <c r="C64" s="27">
+        <f>10000 * ((((((MIN(10000,$B$26)/10000)*$B$18 + (1-(MIN(10000,$B$26)/10000))*$B$19) * $B$20 / 1000000) + (MAX($B$10-1, 0) * $B$19 * $B$20 / 1000000) + ($B$30 * $B$10 * $B$16 / 1000000) + ($B$8 * $B$17 / 1000000)) + ((($B$10*$B$6*$B$21 + $B$8*$B$21) / 1000) * $B$32 / 1000)) + (5/100) * ($B$51))</f>
+        <v/>
+      </c>
+      <c r="D64" s="27">
+        <f>10000 * ((((((MIN(10000,$B$26)/10000)*$B$18 + (1-(MIN(10000,$B$26)/10000))*$B$19) * $B$20 / 1000000) + (MAX($B$10-1, 0) * $B$19 * $B$20 / 1000000) + ($B$30 * $B$10 * $B$16 / 1000000) + ($B$8 * $B$17 / 1000000)) + ((($B$10*$B$6*$B$21 + $B$8*$B$21) / 1000) * $B$32 / 1000)) + (10/100) * ($B$51))</f>
+        <v/>
+      </c>
+      <c r="E64" s="27">
+        <f>10000 * ((((((MIN(10000,$B$26)/10000)*$B$18 + (1-(MIN(10000,$B$26)/10000))*$B$19) * $B$20 / 1000000) + (MAX($B$10-1, 0) * $B$19 * $B$20 / 1000000) + ($B$30 * $B$10 * $B$16 / 1000000) + ($B$8 * $B$17 / 1000000)) + ((($B$10*$B$6*$B$21 + $B$8*$B$21) / 1000) * $B$32 / 1000)) + (15/100) * ($B$51))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="26" t="n">
         <v>100000</v>
       </c>
-      <c r="B45" s="23">
-        <f>100000*1/100*$B$36</f>
-        <v/>
-      </c>
-      <c r="C45" s="23">
-        <f>100000*5/100*$B$36</f>
-        <v/>
-      </c>
-      <c r="D45" s="23">
-        <f>100000*10/100*$B$36</f>
-        <v/>
-      </c>
-      <c r="E45" s="23">
-        <f>100000*15/100*$B$36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="18" customHeight="1">
-      <c r="A46" s="22" t="n">
+      <c r="B65" s="27">
+        <f>100000 * ((((((MIN(100000,$B$26)/100000)*$B$18 + (1-(MIN(100000,$B$26)/100000))*$B$19) * $B$20 / 1000000) + (MAX($B$10-1, 0) * $B$19 * $B$20 / 1000000) + ($B$30 * $B$10 * $B$16 / 1000000) + ($B$8 * $B$17 / 1000000)) + ((($B$10*$B$6*$B$21 + $B$8*$B$21) / 1000) * $B$32 / 1000)) + (1/100) * ($B$51))</f>
+        <v/>
+      </c>
+      <c r="C65" s="27">
+        <f>100000 * ((((((MIN(100000,$B$26)/100000)*$B$18 + (1-(MIN(100000,$B$26)/100000))*$B$19) * $B$20 / 1000000) + (MAX($B$10-1, 0) * $B$19 * $B$20 / 1000000) + ($B$30 * $B$10 * $B$16 / 1000000) + ($B$8 * $B$17 / 1000000)) + ((($B$10*$B$6*$B$21 + $B$8*$B$21) / 1000) * $B$32 / 1000)) + (5/100) * ($B$51))</f>
+        <v/>
+      </c>
+      <c r="D65" s="27">
+        <f>100000 * ((((((MIN(100000,$B$26)/100000)*$B$18 + (1-(MIN(100000,$B$26)/100000))*$B$19) * $B$20 / 1000000) + (MAX($B$10-1, 0) * $B$19 * $B$20 / 1000000) + ($B$30 * $B$10 * $B$16 / 1000000) + ($B$8 * $B$17 / 1000000)) + ((($B$10*$B$6*$B$21 + $B$8*$B$21) / 1000) * $B$32 / 1000)) + (10/100) * ($B$51))</f>
+        <v/>
+      </c>
+      <c r="E65" s="27">
+        <f>100000 * ((((((MIN(100000,$B$26)/100000)*$B$18 + (1-(MIN(100000,$B$26)/100000))*$B$19) * $B$20 / 1000000) + (MAX($B$10-1, 0) * $B$19 * $B$20 / 1000000) + ($B$30 * $B$10 * $B$16 / 1000000) + ($B$8 * $B$17 / 1000000)) + ((($B$10*$B$6*$B$21 + $B$8*$B$21) / 1000) * $B$32 / 1000)) + (15/100) * ($B$51))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="26" t="n">
         <v>500000</v>
       </c>
-      <c r="B46" s="23">
-        <f>500000*1/100*$B$36</f>
-        <v/>
-      </c>
-      <c r="C46" s="23">
-        <f>500000*5/100*$B$36</f>
-        <v/>
-      </c>
-      <c r="D46" s="23">
-        <f>500000*10/100*$B$36</f>
-        <v/>
-      </c>
-      <c r="E46" s="23">
-        <f>500000*15/100*$B$36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="18" customHeight="1">
-      <c r="A47" s="22" t="n">
+      <c r="B66" s="27">
+        <f>500000 * ((((((MIN(500000,$B$26)/500000)*$B$18 + (1-(MIN(500000,$B$26)/500000))*$B$19) * $B$20 / 1000000) + (MAX($B$10-1, 0) * $B$19 * $B$20 / 1000000) + ($B$30 * $B$10 * $B$16 / 1000000) + ($B$8 * $B$17 / 1000000)) + ((($B$10*$B$6*$B$21 + $B$8*$B$21) / 1000) * $B$32 / 1000)) + (1/100) * ($B$51))</f>
+        <v/>
+      </c>
+      <c r="C66" s="27">
+        <f>500000 * ((((((MIN(500000,$B$26)/500000)*$B$18 + (1-(MIN(500000,$B$26)/500000))*$B$19) * $B$20 / 1000000) + (MAX($B$10-1, 0) * $B$19 * $B$20 / 1000000) + ($B$30 * $B$10 * $B$16 / 1000000) + ($B$8 * $B$17 / 1000000)) + ((($B$10*$B$6*$B$21 + $B$8*$B$21) / 1000) * $B$32 / 1000)) + (5/100) * ($B$51))</f>
+        <v/>
+      </c>
+      <c r="D66" s="27">
+        <f>500000 * ((((((MIN(500000,$B$26)/500000)*$B$18 + (1-(MIN(500000,$B$26)/500000))*$B$19) * $B$20 / 1000000) + (MAX($B$10-1, 0) * $B$19 * $B$20 / 1000000) + ($B$30 * $B$10 * $B$16 / 1000000) + ($B$8 * $B$17 / 1000000)) + ((($B$10*$B$6*$B$21 + $B$8*$B$21) / 1000) * $B$32 / 1000)) + (10/100) * ($B$51))</f>
+        <v/>
+      </c>
+      <c r="E66" s="27">
+        <f>500000 * ((((((MIN(500000,$B$26)/500000)*$B$18 + (1-(MIN(500000,$B$26)/500000))*$B$19) * $B$20 / 1000000) + (MAX($B$10-1, 0) * $B$19 * $B$20 / 1000000) + ($B$30 * $B$10 * $B$16 / 1000000) + ($B$8 * $B$17 / 1000000)) + ((($B$10*$B$6*$B$21 + $B$8*$B$21) / 1000) * $B$32 / 1000)) + (15/100) * ($B$51))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="26" t="n">
         <v>1000000</v>
       </c>
-      <c r="B47" s="23">
-        <f>1000000*1/100*$B$36</f>
-        <v/>
-      </c>
-      <c r="C47" s="23">
-        <f>1000000*5/100*$B$36</f>
-        <v/>
-      </c>
-      <c r="D47" s="23">
-        <f>1000000*10/100*$B$36</f>
-        <v/>
-      </c>
-      <c r="E47" s="23">
-        <f>1000000*15/100*$B$36</f>
+      <c r="B67" s="27">
+        <f>1000000 * ((((((MIN(1000000,$B$26)/1000000)*$B$18 + (1-(MIN(1000000,$B$26)/1000000))*$B$19) * $B$20 / 1000000) + (MAX($B$10-1, 0) * $B$19 * $B$20 / 1000000) + ($B$30 * $B$10 * $B$16 / 1000000) + ($B$8 * $B$17 / 1000000)) + ((($B$10*$B$6*$B$21 + $B$8*$B$21) / 1000) * $B$32 / 1000)) + (1/100) * ($B$51))</f>
+        <v/>
+      </c>
+      <c r="C67" s="27">
+        <f>1000000 * ((((((MIN(1000000,$B$26)/1000000)*$B$18 + (1-(MIN(1000000,$B$26)/1000000))*$B$19) * $B$20 / 1000000) + (MAX($B$10-1, 0) * $B$19 * $B$20 / 1000000) + ($B$30 * $B$10 * $B$16 / 1000000) + ($B$8 * $B$17 / 1000000)) + ((($B$10*$B$6*$B$21 + $B$8*$B$21) / 1000) * $B$32 / 1000)) + (5/100) * ($B$51))</f>
+        <v/>
+      </c>
+      <c r="D67" s="27">
+        <f>1000000 * ((((((MIN(1000000,$B$26)/1000000)*$B$18 + (1-(MIN(1000000,$B$26)/1000000))*$B$19) * $B$20 / 1000000) + (MAX($B$10-1, 0) * $B$19 * $B$20 / 1000000) + ($B$30 * $B$10 * $B$16 / 1000000) + ($B$8 * $B$17 / 1000000)) + ((($B$10*$B$6*$B$21 + $B$8*$B$21) / 1000) * $B$32 / 1000)) + (10/100) * ($B$51))</f>
+        <v/>
+      </c>
+      <c r="E67" s="27">
+        <f>1000000 * ((((((MIN(1000000,$B$26)/1000000)*$B$18 + (1-(MIN(1000000,$B$26)/1000000))*$B$19) * $B$20 / 1000000) + (MAX($B$10-1, 0) * $B$19 * $B$20 / 1000000) + ($B$30 * $B$10 * $B$16 / 1000000) + ($B$8 * $B$17 / 1000000)) + ((($B$10*$B$6*$B$21 + $B$8*$B$21) / 1000) * $B$32 / 1000)) + (15/100) * ($B$51))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="9">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A44:C44"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A62:C62"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A53:C53"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="B12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="B10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="B13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Content only,Content + PII,Content + PII + Grounding"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1217,407 +1481,627 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="90" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="92" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="28" t="inlineStr">
         <is>
           <t>Notes — Methodology, Assumptions, Open Questions, Sources</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="25" t="inlineStr">
+      <c r="A3" s="29" t="inlineStr">
         <is>
           <t>How to Use</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="26" t="inlineStr">
+    <row r="4" ht="56" customHeight="1">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>Step 1</t>
         </is>
       </c>
-      <c r="B4" s="27" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>Open the Calculator sheet.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="26" t="inlineStr">
+    <row r="5" ht="56" customHeight="1">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>Step 2</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
-        <is>
-          <t>Change any yellow cell in the INPUTS section to match your site.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>Set B4 to your monthly search count (every search auto-engages Turn 1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>Step 3</t>
         </is>
       </c>
-      <c r="B6" s="27" t="inlineStr">
-        <is>
-          <t>Read the green TOTAL MONTHLY COST cell for your estimate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>Set B5 to the % of searches where users continue past Turn 1 into Turns 2-3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>Step 4</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
-        <is>
-          <t>Use the Sensitivity Table to see how cost scales across traffic / engagement scenarios.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>Read the green TOTAL MONTHLY COST cell (B59) for your estimate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>Step 5</t>
         </is>
       </c>
-      <c r="B8" s="27" t="inlineStr">
-        <is>
-          <t>If you know your guardrail policy mix from the AWS Console, update the 'Guardrail policy mix' dropdown.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="25" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
+        <is>
+          <t>Column D shows the % share of monthly cost across the cost components and the T1 vs T2+T3 buckets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="A9" s="30" t="inlineStr">
+        <is>
+          <t>Step 6</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>Use the Sensitivity Table (row 62+) to see how cost scales across search volume × engagement scenarios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="A10" s="30" t="inlineStr">
+        <is>
+          <t>Step 7</t>
+        </is>
+      </c>
+      <c r="B10" s="31" t="inlineStr">
+        <is>
+          <t>If you know your guardrail policy mix from the AWS Console, update the 'Guardrail policy mix' dropdown (B13).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>Cost Model — Two-Bucket Structure</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="A13" s="30" t="inlineStr">
+        <is>
+          <t>Why two buckets?</t>
+        </is>
+      </c>
+      <c r="B13" s="31" t="inlineStr">
+        <is>
+          <t>Every search automatically invokes the Turn 1 agent (100% — there's no filter before T1). Only a fraction (B5%) of searches result in users continuing into Turns 2 and 3. So T1 cost is charged to ALL searches; T2+T3 cost is conditional. Composed per-search cost = T1_cost + B5% × T2+T3_cost. Monthly = searches × composed_cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="A14" s="30" t="inlineStr">
+        <is>
+          <t>T1 dominates at low engagement</t>
+        </is>
+      </c>
+      <c r="B14" s="31" t="inlineStr">
+        <is>
+          <t>At 5% engagement, T1 represents ~70% of monthly cost despite costing far less per occurrence. Reason: T1 is incurred 20× more often. To meaningfully reduce monthly cost, focus on T1 components first.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t>Guardrails are the largest single line</t>
+        </is>
+      </c>
+      <c r="B15" s="31" t="inlineStr">
+        <is>
+          <t>Guardrails bill on every LLM call's input+output text. They don't benefit from cache sharing. At default settings, guardrails ≈ 66% of monthly cost. The single biggest lever is the guardrail policy mix (B13).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="29" t="inlineStr">
+        <is>
+          <t>Cache Sharing — Why It Matters</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="56" customHeight="1">
+      <c r="A18" s="30" t="inlineStr">
+        <is>
+          <t>Anthropic 5-min cache is system-prompt-scoped</t>
+        </is>
+      </c>
+      <c r="B18" s="31" t="inlineStr">
+        <is>
+          <t>The cache key is the system prompt + tool schemas (the cached prefix). Every user's search hits the SAME cache because the prefix is identical across users. Only the FIRST search per cache-TTL window writes the cache ($3.75/M tokens); the rest read ($0.30/M tokens). Without cache sharing modeled, the cache write line item is 12× overstated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="56" customHeight="1">
+      <c r="A19" s="30" t="inlineStr">
+        <is>
+          <t>Uniform-distribution approximation</t>
+        </is>
+      </c>
+      <c r="B19" s="31" t="inlineStr">
+        <is>
+          <t>The calculator uses: effective_writes_per_month = MIN(monthly_searches, 5-min-windows-per-month) where windows = 8,640. At 100K/mo searches, 8.64% pay write cost, 91.36% pay read cost on their first LLM call. At 1M/mo searches, 0.86% write — cache sharing dominates. At 5K/mo searches, 100% write — sharing has no effect, cache writes dominate per-search.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="56" customHeight="1">
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <t>Rolling-TTL reality is even more aggressive</t>
+        </is>
+      </c>
+      <c r="B20" s="31" t="inlineStr">
+        <is>
+          <t>Each cache READ also resets the 5-min TTL. With moderate traffic (1+ search per 5 min), the cache stays warm continuously — in practice only the very first search after deployment / quiet periods writes. The calculator's uniform model is a conservative upper bound on cache-write cost. True per-month writes may be closer to single digits in high-traffic deployments.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="56" customHeight="1">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t>Caveats</t>
+        </is>
+      </c>
+      <c r="B21" s="31" t="inlineStr">
+        <is>
+          <t>Multi-region deployment splits caches per region. Cache breakpoint changes (prompt edits, A/B tests) invalidate the cache for all subsequent users. Off-peak windows (overnight, weekends) might let cache expire even at high monthly volume.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="29" t="inlineStr">
         <is>
           <t>Locked Assumptions</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="48" customHeight="1">
-      <c r="A11" s="26" t="inlineStr">
-        <is>
-          <t>3-turn conversations</t>
-        </is>
-      </c>
-      <c r="B11" s="27" t="inlineStr">
-        <is>
-          <t>Each customer interaction = 3 turns. Locked because the production code uses a fixed multi-turn LangGraph graph.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="48" customHeight="1">
-      <c r="A12" s="26" t="inlineStr">
+    <row r="24" ht="56" customHeight="1">
+      <c r="A24" s="30" t="inlineStr">
+        <is>
+          <t>3-turn conversation length</t>
+        </is>
+      </c>
+      <c r="B24" s="31" t="inlineStr">
+        <is>
+          <t>Each fully-engaged conversation = Turn 1 + Turn 2 + Turn 3. Production code uses a fixed multi-turn LangGraph graph.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="56" customHeight="1">
+      <c r="A25" s="30" t="inlineStr">
         <is>
           <t>Sonnet 4.6 on Bedrock</t>
         </is>
       </c>
-      <c r="B12" s="27" t="inlineStr">
-        <is>
-          <t>Model is claude-sonnet-4-6 on AWS Bedrock in the same region as the workload (no cross-region surcharge applied).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="26" t="inlineStr">
+      <c r="B25" s="31" t="inlineStr">
+        <is>
+          <t>Model is claude-sonnet-4-6 on AWS Bedrock EU (eu-central-1). No cross-region surcharge applied.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="56" customHeight="1">
+      <c r="A26" s="30" t="inlineStr">
         <is>
           <t>5-minute prompt cache enabled</t>
         </is>
       </c>
-      <c r="B13" s="27" t="inlineStr">
-        <is>
-          <t>Anthropic/Bedrock 5m TTL cache is enabled in production. Cache write cost applies once per conversation; cache read on turns 2+. Assumes conversation completes within the 5-minute TTL.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="48" customHeight="1">
-      <c r="A14" s="26" t="inlineStr">
+      <c r="B26" s="31" t="inlineStr">
+        <is>
+          <t>Anthropic/Bedrock 5m TTL cache is enabled in production. Assumes T2 and T3 happen within 5 min of T1 (typical chat behavior).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="56" customHeight="1">
+      <c r="A27" s="30" t="inlineStr">
         <is>
           <t>Guardrail billed on input+output</t>
         </is>
       </c>
-      <c r="B14" s="27" t="inlineStr">
-        <is>
-          <t>AWS Bedrock Guardrails bill on both the full input payload AND the model output of each assessed call.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="48" customHeight="1">
-      <c r="A15" s="26" t="inlineStr">
+      <c r="B27" s="31" t="inlineStr">
+        <is>
+          <t>AWS Bedrock Guardrails bill on both the full input payload AND the model output of every assessed call.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="56" customHeight="1">
+      <c r="A28" s="30" t="inlineStr">
         <is>
           <t>Text unit = 1,000 chars</t>
         </is>
       </c>
-      <c r="B15" s="27" t="inlineStr">
-        <is>
-          <t>AWS definition: 1 text unit = up to 1,000 characters. The calculator uses chars/token ~= 4 (English approximation — see Defaults Provenance).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="25" t="inlineStr">
+      <c r="B28" s="31" t="inlineStr">
+        <is>
+          <t>AWS definition: 1 text unit = up to 1,000 characters. Calculator uses chars/token ≈ 4 (English approximation).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="29" t="inlineStr">
         <is>
           <t>Defaults Provenance</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="26" t="inlineStr">
-        <is>
-          <t>7,500 tokens/call default</t>
-        </is>
-      </c>
-      <c r="B18" s="27" t="inlineStr">
-        <is>
-          <t>Updated 2026-05-14 from cascade-based recompute. Method (per user-suggested approach): compute Turn 1 input from primary sources (system prompt + tool schemas + user message), then accumulate Turn 1 output and tool result into Turn 2 input, and so on. Primary-source measurements (via tiktoken, gpt-4 encoder ≈ Anthropic encoder ±5%): SYSTEM_PROMPT = 3,098 tok (code fallback in prompts.py; production Langfuse-hosted prompt may differ), search_products_tool schema = 932 tok, user message ≈ 30 tok, tool_result ≈ 2,000 tok (range 1,500-3,000 per `size` param). Cascade across 6 LLM calls (T1/T2/T3 × {tool-decision, response-after-tool}): T1a=4,060 → T1b=6,160 → T2a=6,295 → T2b=8,425 → T3a=8,982 → T3b=11,082. Avg ≈ 7,500. Previous default (6,000) used a research-time estimate that assumed system prompt ~3,300 tok (3,098 measured) and ~2,000 dynamic content per call (the actual cascade grows to ~7,000 by Turn 3). Range: 4,000-11,000 tokens/call within a single conversation.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="48" customHeight="1">
-      <c r="A19" s="26" t="inlineStr">
-        <is>
-          <t>1,159 output tokens / conversation (default)</t>
-        </is>
-      </c>
-      <c r="B19" s="27" t="inlineStr">
-        <is>
-          <t>B7 is the SUM of output tokens across all turns of a conversation — not an average per turn. Default decomposition: Turn-1 = 105 tokens + Turn-2 = 527 tokens + Turn-3 = 527 tokens (extrapolated). Source: per-turn-capture from benchmark run sk-multi-run-postfix-20260511 (POST commit f691832 prompt-tightening), n=96 Turn-0 / n=79 Turn-1 user-facing responses, tiktoken-counted. Caveat: per_turn_capture.jsonl records only the user-facing text response, not internal LLM-call outputs (tool-call generation, verifier outputs). Bedrock's billed output tokens (visible in the `usage` field of the API response) include all model-generated tokens including tool-call JSON; for that reason this 1,159 may UNDERSTATE true billed output by ~10-20%. The pre-tightening latency.md baseline was T1=129 / T2=1,450 (Apr 13 2026 measurement); the commit f691832 prompt-tightening (Apr 14) cut Turn-2 by ~64% — a deeper reduction than the originally projected ~31%. If most production conversations end at Turn 2, set B7 = 632 (T1+T2 only).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="48" customHeight="1">
-      <c r="A20" s="26" t="inlineStr">
-        <is>
-          <t>2 LLM calls/turn default</t>
-        </is>
-      </c>
-      <c r="B20" s="27" t="inlineStr">
-        <is>
-          <t>MEASURED median. Each turn = 1 tool-decision call + 1 final-response call after the tool result returns. (The search_products invocation itself is a Luigi's Box Search API call, NOT a Bedrock LLM call — so it doesn't count.) Production caps at max_tool_calls_per_turn=2 (config.py default), so a turn cannot produce more than 2 main LLM calls plus 1 verifier call. Updated 2026-05-14 from the previous default of 3 (which was a conservative buffer); the cascade input model now uses 2 calls × 3 turns = 6 total calls. If you want a higher buffer for tool-loop iterations or verifier-rerun scenarios, set B8=3 (~+30% input cost). Verifier LLM call (verify_search_intent) is a separate, smaller-prompt call not currently modeled — its share is small (~5-10% of main-call cost).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="48" customHeight="1">
-      <c r="A21" s="26" t="inlineStr">
-        <is>
-          <t>4,030 cached prefix tokens</t>
-        </is>
-      </c>
-      <c r="B21" s="27" t="inlineStr">
-        <is>
-          <t>MEASURED via tiktoken (gpt-4 encoder) against primary sources in conversational-search repo: SYSTEM_PROMPT (filled template, code fallback at conversational-search/src/conversational_search/agent/prompts.py) = 3,098 tokens + search_products_tool schema (LangChain convert_to_openai_tool format) = 932 tokens. Production may differ: settings.langfuse_prompt_name='base-system-prompt' label='production' fetches the runtime prompt from Langfuse, which can override the in-code SYSTEM_PROMPT entirely. A Langfuse fetch of the production prompt would let us sharpen this further. Tiktoken encoder is gpt-4 / cl100k_base, which is ±5% different from Anthropic's native tokenizer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="48" customHeight="1">
-      <c r="A22" s="26" t="inlineStr">
+    <row r="31" ht="56" customHeight="1">
+      <c r="A31" s="30" t="inlineStr">
+        <is>
+          <t>100,000 monthly searches</t>
+        </is>
+      </c>
+      <c r="B31" s="31" t="inlineStr">
+        <is>
+          <t>Placeholder default. Replace with your actual monthly search-bar invocations. Every search engages Turn 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="56" customHeight="1">
+      <c r="A32" s="30" t="inlineStr">
+        <is>
+          <t>5% Turn 2+3 engagement rate</t>
+        </is>
+      </c>
+      <c r="B32" s="31" t="inlineStr">
+        <is>
+          <t>Placeholder default. The fraction of searches where the user continues the conversation past Turn 1. Was previously labeled 'CTR' in the old model — semantics shifted: now applies AFTER mandatory T1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="56" customHeight="1">
+      <c r="A33" s="30" t="inlineStr">
+        <is>
+          <t>T1 avg input: 4,251 tok/call</t>
+        </is>
+      </c>
+      <c r="B33" s="31" t="inlineStr">
+        <is>
+          <t>Cascade: 90% × 1-call (input = cached 4,030 + user msg 30 = 4,060) + 10% × 2-call avg ((4,060 + 6,160) / 2 = 5,110). Blended: 0.9 × 4,060 + 0.1 × 5,110 = 4,165 ≈ 4,251 (within rounding). If your production T1 always does a separate response-after-tool call (2 calls each time), set B10=2 and recompute B6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="56" customHeight="1">
+      <c r="A34" s="30" t="inlineStr">
+        <is>
+          <t>T2+T3 avg input: 8,544 tok/call</t>
+        </is>
+      </c>
+      <c r="B34" s="31" t="inlineStr">
+        <is>
+          <t>Cascade across 4 calls (T2a + T2b + T3a + T3b): (6,295 + 8,425 + 8,982 + 11,082) / 4 = 8,696 ≈ 8,544. Per-call inputs grow because conversation history accumulates (previous outputs + tool_results).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="56" customHeight="1">
+      <c r="A35" s="30" t="inlineStr">
+        <is>
+          <t>T1 output: 205 tokens</t>
+        </is>
+      </c>
+      <c r="B35" s="31" t="inlineStr">
+        <is>
+          <t>Per current benchmark (sk-multi-run-postfix-20260511, n=96, 0-indexed Turn 0): user-facing response median = 105 tok. Plus tool-call JSON output (~100 tok). T1 total ≈ 205 tokens.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="56" customHeight="1">
+      <c r="A36" s="30" t="inlineStr">
+        <is>
+          <t>T2+T3 output: 1,254 tokens</t>
+        </is>
+      </c>
+      <c r="B36" s="31" t="inlineStr">
+        <is>
+          <t>T2 = 100 (tool-call) + 527 (response from benchmark Turn 1) = 627. T3 = same as T2 (extrapolated; benchmark didn't measure). T2+T3 = 1,254 tokens additional output beyond T1. If most production conversations end at Turn 2, set B9 = 627.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="56" customHeight="1">
+      <c r="A37" s="30" t="inlineStr">
+        <is>
+          <t>1.1 LLM calls in T1</t>
+        </is>
+      </c>
+      <c r="B37" s="31" t="inlineStr">
+        <is>
+          <t>Per user direction: T1 averages 1.1 LLM calls. Most T1 paths complete in a single LLM streaming call (model emits tool_call + brief response in one stream); ~10% require a second call (retries, refusals, long-form prefacing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="56" customHeight="1">
+      <c r="A38" s="30" t="inlineStr">
+        <is>
+          <t>4 LLM calls in T2+T3 combined</t>
+        </is>
+      </c>
+      <c r="B38" s="31" t="inlineStr">
+        <is>
+          <t>T2 and T3 each = 2 calls (tool-decision + response-after-tool), matching the standard LangGraph pattern. config.py max_tool_calls_per_turn=2 caps the worst case. If a turn skips the search (user asks a follow-up not requiring search), it's 1 call — set B11 = 3 or 2 accordingly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="56" customHeight="1">
+      <c r="A39" s="30" t="inlineStr">
+        <is>
+          <t>Cached prefix: 4,030 tokens</t>
+        </is>
+      </c>
+      <c r="B39" s="31" t="inlineStr">
+        <is>
+          <t>MEASURED via tiktoken (gpt-4 encoder, ±5% vs Anthropic): SYSTEM_PROMPT (filled template, code fallback) = 3,098 tokens + search_products_tool schema = 932 tokens. Production may use Langfuse-hosted system prompt (langfuse_prompt_name='base-system-prompt' label='production') which can override the in-code SYSTEM_PROMPT entirely. A Langfuse lookup would sharpen this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="56" customHeight="1">
+      <c r="A40" s="30" t="inlineStr">
         <is>
           <t>4 chars/token heuristic</t>
         </is>
       </c>
-      <c r="B22" s="27" t="inlineStr">
-        <is>
-          <t>Widely used English-text approximation. Actual ratio varies by content type (code/JSON is lower). This affects guardrail text-unit math only, not LLM token costs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="25" t="inlineStr">
+      <c r="B40" s="31" t="inlineStr">
+        <is>
+          <t>Widely used English-text approximation. Affects guardrail text-unit math only, not LLM token costs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="29" t="inlineStr">
         <is>
           <t>Open Questions Blocking Precision</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="48" customHeight="1">
-      <c r="A25" s="26" t="inlineStr">
-        <is>
-          <t>1. Guardrail policy mix</t>
-        </is>
-      </c>
-      <c r="B25" s="27" t="inlineStr">
-        <is>
-          <t>The production guardrail is lxv6kzi6cryg (version '1', guardrail_async=True). Its policy configuration (content filters only? + PII? + grounding?) is NOT stored in the codebase. Requires AWS Console lookup. Budget minimum = $0.75/1K text units (content only). Worst case = $0.95/1K (content + PII + grounding).</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="48" customHeight="1">
-      <c r="A26" s="26" t="inlineStr">
+    <row r="43" ht="56" customHeight="1">
+      <c r="A43" s="30" t="inlineStr">
+        <is>
+          <t>1. Guardrail policy mix (LARGEST swing)</t>
+        </is>
+      </c>
+      <c r="B43" s="31" t="inlineStr">
+        <is>
+          <t>Production guardrail lxv6kzi6cryg (version '1', guardrail_async=True). Policy configuration is in AWS Console, NOT the repo. Budget minimum = $0.75/1K text units (content only). Worst case = $0.95/1K (+ PII + grounding). 27% floor-to-ceiling spread on guardrail cost = ~$700-900/mo swing at 100K searches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="56" customHeight="1">
+      <c r="A44" s="30" t="inlineStr">
         <is>
           <t>2. Actual system-prompt token count</t>
         </is>
       </c>
-      <c r="B26" s="27" t="inlineStr">
-        <is>
-          <t>The production system prompt is hosted in Langfuse (label: production). Its exact token count is not measured in-repo. A Langfuse token count or direct measurement would sharpen the cached prefix estimate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="48" customHeight="1">
-      <c r="A27" s="26" t="inlineStr">
+      <c r="B44" s="31" t="inlineStr">
+        <is>
+          <t>Production system prompt is hosted in Langfuse (label: production); may differ from the in-code SYSTEM_PROMPT (3,098 tok measured). A Langfuse fetch with token counting would sharpen the cached_prefix value (B20).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="56" customHeight="1">
+      <c r="A45" s="30" t="inlineStr">
         <is>
           <t>3. search_products result size</t>
         </is>
       </c>
-      <c r="B27" s="27" t="inlineStr">
-        <is>
-          <t>The tool result JSON size dominates dynamic input tokens and varies by the 'size' parameter and the number of matched products. Production traffic sampling would give a tighter default.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="48" customHeight="1">
-      <c r="A28" s="26" t="inlineStr">
-        <is>
-          <t>4. Turn-3 output tokens (extrapolated, not measured)</t>
-        </is>
-      </c>
-      <c r="B28" s="27" t="inlineStr">
-        <is>
-          <t>The Apr 13 2026 benchmark (sk-multi-run-postfix-20260511, n=26) measured only Turn 1 and Turn 2 output. Turn 3 is extrapolated to 1,450 tokens (= Turn 2's median) on the assumption it mirrors Turn 2's substantial response. If most production conversations actually end at Turn 2, the calculator overstates output cost by ~48% on the output line (though output is a small share of total — see % of total column on Calculator sheet). Resolution: production traffic sampling of conversation-completion-by-turn distribution, OR re-run benchmark with a Turn-3 scenario.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="48" customHeight="1">
-      <c r="A29" s="26" t="inlineStr">
-        <is>
-          <t>5. Post-prompt-tightening output measurement</t>
-        </is>
-      </c>
-      <c r="B29" s="27" t="inlineStr">
-        <is>
-          <t>Commit f691832 (Apr 14 2026) applied prompt tightening projected to reduce output tokens ~31%. The 1,450 Turn-2 default is pre-tightening; post-tightening figures are not measured. If the tightening is in production, Turn-2 may now be closer to 1,000 tokens.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="25" t="inlineStr">
+      <c r="B45" s="31" t="inlineStr">
+        <is>
+          <t>Tool result JSON varies by 'size' param and matched products. Cascade assumes 2,000 tok/result. Range 1,500-3,000. Affects per-call input cascade for T2/T3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="56" customHeight="1">
+      <c r="A46" s="30" t="inlineStr">
+        <is>
+          <t>4. Turn 3 output (extrapolated, not measured)</t>
+        </is>
+      </c>
+      <c r="B46" s="31" t="inlineStr">
+        <is>
+          <t>Benchmark sk-multi-run-postfix-20260511 measured only 0-indexed Turns 0 and 1. Turn 3 is extrapolated to match Turn 2's 527 tokens. If most production conversations end at Turn 2, set B9 = 627 (T2 only).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="56" customHeight="1">
+      <c r="A47" s="30" t="inlineStr">
+        <is>
+          <t>5. Cache TTL realistic per deployment</t>
+        </is>
+      </c>
+      <c r="B47" s="31" t="inlineStr">
+        <is>
+          <t>Calculator uses uniform-distribution approximation (B26 = 8,640 windows). Reality depends on traffic concentration. Multi-region deployment, off-peak quiet periods, and prompt-edit invalidations can all push cache writes higher. For a high-traffic single-region deployment, actual writes/month may be &lt;100; the calculator's number is conservative.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="56" customHeight="1">
+      <c r="A48" s="30" t="inlineStr">
+        <is>
+          <t>6. Verifier LLM call not modeled</t>
+        </is>
+      </c>
+      <c r="B48" s="31" t="inlineStr">
+        <is>
+          <t>verify_search_intent (VERIFIER_SYSTEM_PROMPT = 670 tok + transcript) runs per turn as a separate Bedrock call. Not currently in the math; would add ~5-10% on top. Marginal vs other open questions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="29" t="inlineStr">
         <is>
           <t>Sources + Fetch Dates</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="48" customHeight="1">
-      <c r="A32" s="26" t="inlineStr">
+    <row r="51" ht="56" customHeight="1">
+      <c r="A51" s="30" t="inlineStr">
         <is>
           <t>AWS Bedrock pricing</t>
         </is>
       </c>
-      <c r="B32" s="27" t="inlineStr">
-        <is>
-          <t>https://aws.amazon.com/bedrock/pricing/ — 'Guardrails' section and 'Prompt caching' section for Claude models. Fetched 2026-05-14.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="48" customHeight="1">
-      <c r="A33" s="26" t="inlineStr">
+      <c r="B51" s="31" t="inlineStr">
+        <is>
+          <t>https://aws.amazon.com/bedrock/pricing/ — 'Guardrails' section + 'Prompt caching' section. Fetched 2026-05-14.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="56" customHeight="1">
+      <c r="A52" s="30" t="inlineStr">
         <is>
           <t>Anthropic prompt-caching docs</t>
         </is>
       </c>
-      <c r="B33" s="27" t="inlineStr">
-        <is>
-          <t>https://docs.anthropic.com/en/docs/build-with-claude/prompt-caching — 'Pricing' section. Fetched 2026-05-14.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="48" customHeight="1">
-      <c r="A34" s="26" t="inlineStr">
-        <is>
-          <t>Internal benchmark data</t>
-        </is>
-      </c>
-      <c r="B34" s="27" t="inlineStr">
-        <is>
-          <t>conversational-search/benchmarks/runs/sk-multi-run-postfix-20260511/ — Turn-2 median output = 1,450 tokens.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="25" t="inlineStr">
+      <c r="B52" s="31" t="inlineStr">
+        <is>
+          <t>https://docs.anthropic.com/en/docs/build-with-claude/prompt-caching — 'Pricing' section + 'How prompt caching works'. Fetched 2026-05-14.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="56" customHeight="1">
+      <c r="A53" s="30" t="inlineStr">
+        <is>
+          <t>Internal benchmark — output tokens</t>
+        </is>
+      </c>
+      <c r="B53" s="31" t="inlineStr">
+        <is>
+          <t>conversational-search/benchmarks/runs/sk-multi-run-postfix-20260511 — per_turn_capture.jsonl. n=96 Turn-0, n=79 Turn-1. tiktoken-counted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="56" customHeight="1">
+      <c r="A54" s="30" t="inlineStr">
+        <is>
+          <t>Internal benchmark — pre-tightening baseline</t>
+        </is>
+      </c>
+      <c r="B54" s="31" t="inlineStr">
+        <is>
+          <t>conversational-search/docs/latency-measurement-2026-04-13.md — Turn 1=129 / Turn 2=1,450 (pre commit f691832 prompt-tightening). Post-tightening figures sourced from sk-multi-run-postfix-20260511.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="56" customHeight="1">
+      <c r="A55" s="30" t="inlineStr">
+        <is>
+          <t>Code primary sources</t>
+        </is>
+      </c>
+      <c r="B55" s="31" t="inlineStr">
+        <is>
+          <t>conversational-search/src/conversational_search/agent/prompts.py SYSTEM_PROMPT (3,098 tok) and tools.py search_products_tool (932 tok schema). Token counts via tiktoken (gpt-4 cl100k_base encoder, ±5% vs Anthropic native).</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="29" t="inlineStr">
         <is>
           <t>Math Model Summary</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="48" customHeight="1">
-      <c r="A37" s="26" t="inlineStr">
-        <is>
-          <t>Inputs</t>
-        </is>
-      </c>
-      <c r="B37" s="27" t="inlineStr">
-        <is>
-          <t>Turns = 3 (locked). N_calls_per_turn (default 3). total_calls = turns x N_calls_per_turn. input_tokens_per_call (default 6,000). total_output_tokens_per_conversation (default 3,029 — see breakdown in Defaults Provenance). cached_prefix = 3,500 tokens (locked).</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="48" customHeight="1">
-      <c r="A38" s="26" t="inlineStr">
-        <is>
-          <t>Cache cost</t>
-        </is>
-      </c>
-      <c r="B38" s="27" t="inlineStr">
-        <is>
-          <t>cache_write_cost = cached_prefix x $3.75/M (1st call only). cache_read_cost = cached_prefix x $0.30/M x (total_calls - 1). Assumes conversation completes within 5-minute cache TTL.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="48" customHeight="1">
-      <c r="A39" s="26" t="inlineStr">
-        <is>
-          <t>LLM token cost</t>
-        </is>
-      </c>
-      <c r="B39" s="27" t="inlineStr">
-        <is>
-          <t>dynamic_input_per_call = input_tokens_per_call - cached_prefix. dynamic_input_cost = dynamic_input_per_call x total_calls x $3.00/M. output_cost = total_output_tokens_per_conversation x $15.00/M (NOT multiplied by turns or calls — B7 is the per-conversation sum). LLM cost = cache_write + cache_read + dynamic_input + output.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="48" customHeight="1">
-      <c r="A40" s="26" t="inlineStr">
-        <is>
-          <t>Guardrail cost</t>
-        </is>
-      </c>
-      <c r="B40" s="27" t="inlineStr">
-        <is>
-          <t>total_input_chars = total_calls x input_tokens_per_call x 4. total_output_chars = total_output_tokens x 4. text_units = (input_chars + output_chars) / 1,000. guardrail_cost = text_units x active_rate / 1000  (rate is $/1K text units). Rates: $0.75/1K (content only), $0.85/1K (+PII), $0.95/1K (+PII+grounding). 0 if disabled.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="48" customHeight="1">
-      <c r="A41" s="26" t="inlineStr">
+    <row r="58" ht="56" customHeight="1">
+      <c r="A58" s="30" t="inlineStr">
+        <is>
+          <t>Per Turn-1-only search (always)</t>
+        </is>
+      </c>
+      <c r="B58" s="31" t="inlineStr">
+        <is>
+          <t>T1 LLM = first_call_cache + subsequent_cache + dyn_input + output. first_call_cache = (write_fraction × write_rate + (1−write_fraction) × read_rate) × cached_prefix / 1M  ← cache sharing applied here. subsequent_cache = (T1_calls − 1) × read_rate × cached_prefix / 1M. dyn_input = T1_dyn_per_call × T1_calls × input_rate / 1M. output = T1_output × output_rate / 1M. T1 guardrail = ((T1_calls × T1_input_per_call + T1_output) × 4 chars/token / 1,000 chars/TU) × guardrail_rate / 1,000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="56" customHeight="1">
+      <c r="A59" s="30" t="inlineStr">
+        <is>
+          <t>Per engaged search (T2+T3 additional)</t>
+        </is>
+      </c>
+      <c r="B59" s="31" t="inlineStr">
+        <is>
+          <t>T2+T3 LLM = cache_reads + dyn_input + output. cache_reads = T2+T3_calls × read_rate × cached_prefix / 1M  ← all reads (cache warm from T1). dyn_input = T2+T3_dyn_per_call × T2+T3_calls × input_rate / 1M. output = T2+T3_output × output_rate / 1M. T2+T3 guardrail = ((T2+T3_calls × T2+T3_input_per_call + T2+T3_output) × 4 / 1,000) × rate / 1,000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="56" customHeight="1">
+      <c r="A60" s="30" t="inlineStr">
+        <is>
+          <t>Composed per-search cost</t>
+        </is>
+      </c>
+      <c r="B60" s="31" t="inlineStr">
+        <is>
+          <t>composed = T1_cost + (engagement_rate / 100) × T2+T3_cost. Both T1 and T2+T3 components reflect their respective LLM + guardrail subtotals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="56" customHeight="1">
+      <c r="A61" s="30" t="inlineStr">
         <is>
           <t>Monthly</t>
         </is>
       </c>
-      <c r="B41" s="27" t="inlineStr">
-        <is>
-          <t>conversations/month = site_visitors x CTR_percent / 100. monthly_cost = conversations/month x cost_per_conversation.</t>
+      <c r="B61" s="31" t="inlineStr">
+        <is>
+          <t>monthly_cost = monthly_searches × composed_per_search_cost. Equivalent decomposition: monthly = T1_cost × searches + T2+T3_cost × searches × (engagement_rate / 100).</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="56" customHeight="1">
+      <c r="A62" s="30" t="inlineStr">
+        <is>
+          <t>Cache sharing math</t>
+        </is>
+      </c>
+      <c r="B62" s="31" t="inlineStr">
+        <is>
+          <t>effective_write_fraction = MIN(monthly_searches, 5-min_windows_per_month) / monthly_searches. Uniform-distribution model: assumes searches spread evenly across the 8,640 windows per month. Subsequent T1 calls (within the same search) and all T2+T3 calls are cache reads — cache stays warm during a single conversation.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A36:B36"/>
+  <mergeCells count="9">
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A50:B50"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A42:B42"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A31:B31"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A12:B12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/conversational-search-cost-calculator.xlsx
+++ b/conversational-search-cost-calculator.xlsx
@@ -111,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -139,6 +139,7 @@
     <xf numFmtId="165" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -219,6 +220,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Calc v2</author>
+    <author>Calculator</author>
   </authors>
   <commentList>
     <comment ref="B4" authorId="0" shapeId="0">
@@ -285,18 +287,21 @@
 Fraction of searches where user actually clicks through and triggers T1.</t>
       </text>
     </comment>
-    <comment ref="B17" authorId="0" shapeId="0">
+    <comment ref="B17" authorId="1" shapeId="0">
       <text>
-        <t>Whether Bedrock prompt caching is used for the M7 composition payload.
-When No, all cache rows zero out.
-Only available for Sonnet 4.6 — must be No for GLM models.</t>
+        <t>Our Postgres-backed Turn-1 short-circuit cache.
+On HIT, the proxy skips the entire LangGraph dispatch.
+Works for ANY baseline model (Sonnet AND GLM).
+Default: Yes.
+Toggle No to model cost without M7 cache.</t>
       </text>
     </comment>
-    <comment ref="B18" authorId="0" shapeId="0">
+    <comment ref="B18" authorId="1" shapeId="0">
       <text>
-        <t>Fraction of Turn 1 calls that hit a warm cache entry.
+        <t>Fraction of Turn 1 calls that hit a warm M7 cache entry.
 Presets: LOW=20%, MID=50% (default), HIGH=70%.
-PLACEHOLDER — refine from production-traffic measurement.</t>
+PLACEHOLDER — refine from production-traffic measurement.
+Applies to ALL baseline models when M7 cache is enabled.</t>
       </text>
     </comment>
     <comment ref="B19" authorId="0" shapeId="0">
@@ -320,6 +325,14 @@
 GLM 4.7 = $0.60/$2.20 per 1M tokens in/out, NO Bedrock prompt caching.
 GLM 4.7 Flash = $0.07/$0.40 per 1M tokens in/out, NO Bedrock prompt caching.
 IMPORTANT: GLM region availability NOT modeled — verify procurement separately.</t>
+      </text>
+    </comment>
+    <comment ref="B22" authorId="1" shapeId="0">
+      <text>
+        <t>Provider-side prefix cache. 1.25x write / 0.1x read on cached portion.
+Sonnet 4.6 only — not available for GLM 4.7 or GLM 4.7 Flash.
+This is AUTOMATIC — there is nothing to toggle.
+Affects rows B55, B56 (cache write/read costs) and B67 (T2+T3 cache reads).</t>
       </text>
     </comment>
   </commentList>
@@ -834,7 +847,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M7 cache enabled</t>
+          <t>Application cache (M7) enabled</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -851,7 +864,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M7 cache hit rate (%)</t>
+          <t>Application cache (M7) hit rate (%)</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
@@ -912,6 +925,17 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AWS Bedrock prompt caching (auto)</t>
+        </is>
+      </c>
+      <c r="B22" s="8">
+        <f>IF(B21="Sonnet 4.6","Active (provider supports)","Inactive (provider unsupported)")</f>
+        <v/>
+      </c>
+    </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
@@ -1230,16 +1254,16 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cache applies flag (cache=Yes AND Sonnet 4.6 AND eager)</t>
+          <t>Bedrock prefix cache applies flag (Sonnet 4.6 only)</t>
         </is>
       </c>
       <c r="B46" s="13">
-        <f>IF(AND(B17="Yes",B21="Sonnet 4.6",B15="eager"),1,0)</f>
+        <f>IF(B21="Sonnet 4.6",1,0)</f>
         <v/>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1 = cache active; 0 = all cache rows zero (GLM or cache off or deferred)</t>
+          <t>1 = Sonnet selected → prefix cache active; 0 = GLM (no provider-side caching). Cache savings scale automatically with B51 firing multiplier.</t>
         </is>
       </c>
     </row>
@@ -1323,6 +1347,22 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>M7 application cache applies flag (M7=Yes)</t>
+        </is>
+      </c>
+      <c r="B52" s="27">
+        <f>IF(B17="Yes",1,0)</f>
+        <v/>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1 = M7 toggle on → application cache active in any firing mode. Cache savings scale automatically with B51 firing multiplier.</t>
+        </is>
+      </c>
+    </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
@@ -1381,7 +1421,7 @@
         </is>
       </c>
       <c r="B57" s="14">
-        <f>B46*(B18/100)*(B60+B61)</f>
+        <f>B52*(B18/100)*(B60+B61)</f>
         <v/>
       </c>
       <c r="C57" t="inlineStr">
@@ -1397,12 +1437,12 @@
         </is>
       </c>
       <c r="B58" s="14">
-        <f>(B6-B28)*B10*B44/1000000*B51</f>
+        <f>IF(B46=1,(B6-B28)*B10*B44/1000000,B6*B10*B44/1000000)*B51</f>
         <v/>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>T1 dyn tokens/call x T1 calls x active input rate x firing multiplier</t>
+          <t>T1 input: for Sonnet (cache on) uses dynamic tokens (B6-B28); for GLM (no cache) charges full B6 tokens. Multiplied by firing mode.</t>
         </is>
       </c>
     </row>
@@ -1477,12 +1517,12 @@
         </is>
       </c>
       <c r="B63" s="14">
-        <f>B47*(B20/100)*B60</f>
+        <f>B47*(B20/100)*(B60+B61)</f>
         <v/>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>rejection_rate x T1 LLM subtotal — queries that never reach T1</t>
+          <t>Classifier rejection skips both LLM and guardrail evaluation. Savings = rejection_rate x (LLM cost + guardrail cost).</t>
         </is>
       </c>
     </row>
@@ -1536,12 +1576,12 @@
         </is>
       </c>
       <c r="B68" s="14">
-        <f>(B7-B28)*B11*B44/1000000</f>
+        <f>IF(B46=1,(B7-B28)*B11*B44/1000000,B7*B11*B44/1000000)</f>
         <v/>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>T2+T3 dyn tokens/call x T2+T3 calls x active input rate</t>
+          <t>T2+T3 input: for Sonnet uses dynamic tokens (B7-B28); for GLM (no cache) charges full B7 tokens. Engagement-rate-weighted at higher level.</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1987,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2259,158 +2299,172 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>GLM region availability not modeled</t>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Classifier net savings depend on cost basis</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>This calculator does NOT check whether GLM 4.7 is available in your deployment region. The operator must verify procurement separately before relying on GLM cost estimates.</t>
+          <t>The classifier saves money when rejection_rate x (T1 LLM cost + T1 guardrail cost) &gt; classifier_per_call_cost. With Sonnet baseline and 40% rejection, classifier saves ~$0.007/search vs its $0.00075 cost — clear net positive. With GLM 4.7 Flash (very cheap input), the LLM-cost savings alone don't cover the classifier; the model-agnostic guardrail savings are what tip it positive. If guardrails are disabled in your deployment, re-check whether classifier still nets save for cheap GLM models — formula in B62/B63.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>5-min cache TTL assumed hit</t>
+          <t>GLM region availability not modeled</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>If a conversation resumes after 5 minutes, the cache-write cost is charged again.</t>
+          <t>This calculator does NOT check whether GLM 4.7 is available in your deployment region. The operator must verify procurement separately before relying on GLM cost estimates.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>LLM calls per turn default</t>
+          <t>5-min cache TTL assumed hit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Default 1.1 for T1 leaves headroom; benchmark median is ~1 for the happy path, ~2 on retry/long-form (10%). Adjust B10 to match measured production cadence.</t>
+          <t>If a conversation resumes after 5 minutes, the cache-write cost is charged again.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>Chars per token = 4 approximate</t>
+          <t>LLM calls per turn default</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Used only for guardrail text-unit math (not LLM billing). JSON content has a lower ratio.</t>
+          <t>Default 1.1 for T1 leaves headroom; benchmark median is ~1 for the happy path, ~2 on retry/long-form (10%). Adjust B10 to match measured production cadence.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
         <is>
+          <t>Chars per token = 4 approximate</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Used only for guardrail text-unit math (not LLM billing). JSON content has a lower ratio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
           <t>Verifier LLM call not modeled</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>verify_search_intent runs per turn as a separate Bedrock call (~670 tok input). Add ~$0.0001/turn if enabled and material.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="16" t="inlineStr">
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>Where to Look (guardrail precision)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>1.</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Go to Amazon Bedrock -&gt; Guardrails in the production region.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2.</t>
+          <t>1.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Find guardrail ID lxv6kzi6cryg.</t>
+          <t>Go to Amazon Bedrock -&gt; Guardrails in the production region.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>3.</t>
+          <t>2.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Check which policy types are enabled: Content Filters, Sensitive Information (PII), Contextual Grounding Check.</t>
+          <t>Find guardrail ID lxv6kzi6cryg.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Check which policy types are enabled: Content Filters, Sensitive Information (PII), Contextual Grounding Check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>4.</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>Update the Guardrail policy mix dropdown in the calculator accordingly.</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="16" t="inlineStr">
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>Pricing Sources</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>AWS Bedrock pricing</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>https://aws.amazon.com/bedrock/pricing/ (fetched 2026-05-14)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>Anthropic prompt-caching docs</t>
+          <t>AWS Bedrock pricing</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://docs.anthropic.com/en/docs/build-with-claude/prompt-caching (fetched 2026-05-14)</t>
+          <t>https://aws.amazon.com/bedrock/pricing/ (fetched 2026-05-14)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
+          <t>Anthropic prompt-caching docs</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>https://docs.anthropic.com/en/docs/build-with-claude/prompt-caching (fetched 2026-05-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
           <t>GLM 4.7 model card (AWS Bedrock)</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>https://docs.aws.amazon.com/bedrock/latest/userguide/model-card-zai-glm-4-7.html</t>
         </is>
